--- a/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar1_Q80_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar1_Q80_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001307783109237708</v>
+        <v>0.001253476207939622</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001307783109237708</v>
+        <v>0.001253476207939622</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008185573210816463</v>
+        <v>0.0008822259073809841</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002428355712278609</v>
+        <v>0.002396070180980607</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002428355712278609</v>
+        <v>0.002396070180980607</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008558300712698231</v>
+        <v>0.0008877759250321705</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.00504586029526603</v>
+        <v>0.004962879858276035</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00504586029526603</v>
+        <v>0.004962879858276035</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001738013873200822</v>
+        <v>0.001961027168007632</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.008424071676651787</v>
+        <v>0.008305114996941487</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008424071676651787</v>
+        <v>0.008305114996941487</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002585605409837416</v>
+        <v>0.002787262200378574</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01022906052203887</v>
+        <v>0.01008800284793114</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01022906052203887</v>
+        <v>0.01008800284793114</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003222806019374161</v>
+        <v>0.003536118042336425</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.009937590871451142</v>
+        <v>0.009781722085926344</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009937590871451142</v>
+        <v>0.009781722085926344</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003162711156684577</v>
+        <v>0.003434188730806476</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.008908793819935224</v>
+        <v>0.008775628272582112</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008908793819935224</v>
+        <v>0.008775628272582112</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002808494037826753</v>
+        <v>0.00309833327140653</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.008144714477122393</v>
+        <v>0.008034166723872433</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008144714477122393</v>
+        <v>0.008034166723872433</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002559874506758624</v>
+        <v>0.002910205384672798</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.007955718490174558</v>
+        <v>0.007856935159142072</v>
       </c>
       <c r="C10" t="n">
-        <v>0.007955718490174558</v>
+        <v>0.007856935159142072</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002433323245473823</v>
+        <v>0.00277149136858544</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.007170160467697001</v>
+        <v>0.007095189377829299</v>
       </c>
       <c r="C11" t="n">
-        <v>0.007170160467697001</v>
+        <v>0.007095189377829299</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002325457729054254</v>
+        <v>0.002663740300046625</v>
       </c>
     </row>
   </sheetData>
